--- a/results/TFL/tablas/tabla1_fiabilidad_inter_iteraciones.xlsx
+++ b/results/TFL/tablas/tabla1_fiabilidad_inter_iteraciones.xlsx
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gemma-4-31B-it (Local)</t>
+          <t>Gemma-4-31B-it</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -474,27 +474,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>112/114</t>
+          <t>107/114</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>98.25%</t>
+          <t>93.86%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>99.9567%</t>
+          <t>99.8294%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.9994</t>
+          <t>0.9976</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.9983</t>
+          <t>0.9940</t>
         </is>
       </c>
     </row>
@@ -514,34 +514,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>112/114</t>
+          <t>102/114</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>98.25%</t>
+          <t>89.47%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>99.9567%</t>
+          <t>99.6589%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.9994</t>
+          <t>0.9952</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.9983</t>
+          <t>0.9882</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gemini Flash 3.6 (Cloud)</t>
+          <t>Gemini Flash 3.7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -554,27 +554,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>114/114</t>
+          <t>108/114</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>94.74%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>100.0000%</t>
+          <t>99.8538%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.9980</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.9948</t>
         </is>
       </c>
     </row>
